--- a/basedatos_partidas/salida/descompuestos/CT-06-06-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-06-030.xlsx
@@ -539,10 +539,10 @@
         <v>3.2</v>
       </c>
       <c r="G10" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="H10" t="n">
-        <v>4.32</v>
+        <v>3.52</v>
       </c>
     </row>
     <row r="11">
@@ -565,10 +565,10 @@
         <v>5.4</v>
       </c>
       <c r="G11" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>7.29</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>0.026</v>
       </c>
       <c r="G12" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="H12" t="n">
-        <v>3.43</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="13">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>18.01</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="17">
@@ -880,10 +880,10 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>24.59</v>
+        <v>22.83</v>
       </c>
       <c r="H27" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="28">
@@ -899,7 +899,7 @@
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
-        <v>24.84</v>
+        <v>23.06</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-06-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-06-030.xlsx
@@ -643,10 +643,10 @@
         <v>0.6</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="H14" t="n">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="15">
@@ -669,10 +669,10 @@
         <v>0.4</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="H15" t="n">
-        <v>1.24</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="16">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>16.25</v>
+        <v>15.93</v>
       </c>
     </row>
     <row r="17">
@@ -880,7 +880,7 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>22.83</v>
+        <v>22.51</v>
       </c>
       <c r="H27" t="n">
         <v>0.23</v>
@@ -899,7 +899,7 @@
       </c>
       <c r="G28" s="4" t="n"/>
       <c r="H28" s="5" t="n">
-        <v>23.06</v>
+        <v>22.74</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-06-06-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-06-06-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H28"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 06 Paredes y tabiquería</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Mampostería estructural</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
